--- a/docs/admission-crm-comparison.xlsx
+++ b/docs/admission-crm-comparison.xlsx
@@ -8,6 +8,8 @@
     <sheet name="Missing from Main (TODO)" sheetId="3" r:id="rId3"/>
     <sheet name="Missing from omm-dev" sheetId="4" r:id="rId4"/>
     <sheet name="Sub-Module Status" sheetId="5" r:id="rId5"/>
+    <sheet name="Workflows &amp; Impl Guide" sheetId="6" r:id="rId6"/>
+    <sheet name="Architecture Reference" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,12 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D13"/>
-  <cols>
-    <col min="1" max="1" width="27.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -601,14 +597,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F461"/>
-  <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="41.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9840,14 +9828,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F132"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="43.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12499,13 +12479,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E37"/>
-  <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13146,17 +13119,3486 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J108"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sub-Module</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Pages (main)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Pages (omm-dev)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Components</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Services</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Hooks</v>
+      </c>
+      <c r="G1" t="str">
+        <v>API Routes</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Total (main)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Total (omm-dev)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>actions</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G2" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>activities</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>agentic-query</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="E4" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ai-responses</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ai-suggested-responses</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>alerts</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>analytics</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>applications</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>apply</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E10" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>assignment-rules</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>b2a-bridge</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E12" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G12" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>bridge</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E13" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>briefing</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>briefing-notification-banner</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>briefing-popup</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E16" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>calls</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E17" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F17" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="G17" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="H17">
+        <v>7</v>
+      </c>
+      <c r="I17">
+        <v>7</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>campaign-monitoring</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="str">
+        <v>5 vs 5</v>
+      </c>
+      <c r="E18" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G18" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>campaigns</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E19" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5 vs 5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>5 vs 5</v>
+      </c>
+      <c r="H19">
+        <v>14</v>
+      </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>chat</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F20" t="str">
+        <v>8 vs 8</v>
+      </c>
+      <c r="G20" t="str">
+        <v>15 vs 18</v>
+      </c>
+      <c r="H20">
+        <v>23</v>
+      </c>
+      <c r="I20">
+        <v>32</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>chatbot</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E21" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F21" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="G21" t="str">
+        <v>6 vs 6</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>13</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>communication</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>consultants</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>8</v>
+      </c>
+      <c r="D23" t="str">
+        <v>6 vs 6</v>
+      </c>
+      <c r="E23" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2 vs 1</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="H23">
+        <v>19</v>
+      </c>
+      <c r="I23">
+        <v>18</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>core</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1 vs 2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>core-layout</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E25" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>costs</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E26" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F26" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G26" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>counselors</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="str">
+        <v>7 vs 7</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="G27" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
+      </c>
+      <c r="I27">
+        <v>16</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>dashboard</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E28" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F28" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G28" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>data-profiling</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E29" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F29" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G29" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>data-quality</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G30" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>deduplication</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E31" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F31" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>documentation</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E32" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F32" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G32" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>documents</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E33" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F33" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G33" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>drip-sequence-status</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E34" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F34" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G34" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>echo-bubble</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E35" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F35" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G35" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>email</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E36" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F36" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G36" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>expos</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E37" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="G37" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" t="str">
+        <v>main only</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>feedback</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E38" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G38" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
+        <v>6</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>gd-pi</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E39" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F39" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G39" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>gdpi</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E40" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F40" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G40" t="str">
+        <v>0 vs 4</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>group-dashboard</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="E41" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F41" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G41" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>7</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>hostels</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E42" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G42" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>index</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E43" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F43" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G43" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>insights</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="str">
+        <v>8 vs 8</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="F44" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="G44" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H44">
+        <v>15</v>
+      </c>
+      <c r="I44">
+        <v>15</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>interviews</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E45" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F45" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G45" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>lateral-entry</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E46" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F46" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G46" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>lead-scoring</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="E47" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F47" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G47" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H47">
+        <v>6</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>leads</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="E48" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F48" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G48" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H48">
+        <v>9</v>
+      </c>
+      <c r="I48">
+        <v>9</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>loans</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E49" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F49" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G49" t="str">
+        <v>0 vs 4</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>7</v>
+      </c>
+      <c r="J49" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>marketing/campaigns</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E50" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F50" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G50" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>marketing/chat</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="E51" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F51" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G51" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H51">
+        <v>6</v>
+      </c>
+      <c r="I51">
+        <v>6</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>marketing/chatbot</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E52" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F52" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G52" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H52">
+        <v>3</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>marketing/database</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="str">
+        <v>4 vs 0</v>
+      </c>
+      <c r="E53" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="F53" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="G53" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H53">
+        <v>7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>main only</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>marketing/expos</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="str">
+        <v>7 vs 0</v>
+      </c>
+      <c r="E54" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F54" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G54" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H54">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>main only</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>marketing/parent-communication</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="E55" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F55" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G55" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55">
+        <v>3</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>marketing/publishers</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="E56" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F56" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G56" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>marketing/re-engagement</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="E57" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F57" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G57" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H57">
+        <v>3</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>marketing/remarketing</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E58" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F58" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G58" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>marketing/voice-agents</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E59" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F59" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G59" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>marketing/voice-broadcast</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E60" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F60" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G60" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>mcp-tools</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E61" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F61" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G61" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>merit-list</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E62" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F62" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G62" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>5</v>
+      </c>
+      <c r="J62" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>migration-activity_alert_tables</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E63" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F63" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G63" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>migration-add_referral_type</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E64" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F64" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G64" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>main only</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>migration-admission_ai_insights_rls</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E65" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F65" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G65" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>migration-admission_daily_briefings_rls</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E66" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F66" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G66" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>migration-consultant_tables</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E67" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F67" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G67" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>migration-core_tables</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E68" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F68" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G68" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>migration-counselor_daily_view_function</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E69" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F69" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G69" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>migration-enums_and_functions</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E70" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F70" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G70" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>migration-rls_policies</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E71" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F71" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G71" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>migration-triggers_and_views</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E72" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F72" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G72" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>migration-wa_conversations_messages</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E73" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F73" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G73" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>migrations</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E74" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F74" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G74" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H74">
+        <v>3</v>
+      </c>
+      <c r="I74">
+        <v>9</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>naac-report</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E75" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F75" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G75" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H75">
+        <v>2</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>offer-letter</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E76" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F76" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G76" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>other</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E77" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F77" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G77" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>parent-communication</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E78" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F78" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G78" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>5</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>phone-validation</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E79" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F79" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G79" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>process-excellence</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="E80" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F80" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G80" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>publishers</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E81" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F81" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G81" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>4</v>
+      </c>
+      <c r="J81" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>re-engagement</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E82" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F82" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G82" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>5</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>remarketing</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E83" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F83" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G83" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H83">
+        <v>2</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>reminders</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E84" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F84" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G84" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>response-personalizer</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="E85" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F85" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G85" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>scholarships</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E86" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F86" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G86" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>4</v>
+      </c>
+      <c r="J86" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>scoring-rules</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E87" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F87" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G87" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>6</v>
+      </c>
+      <c r="J87" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>screening-exam</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E88" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F88" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G88" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>seat-confirmation</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E89" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="F89" t="str">
+        <v>0 vs 1</v>
+      </c>
+      <c r="G89" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>6</v>
+      </c>
+      <c r="J89" t="str">
+        <v>omm-dev only</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>settings</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E90" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F90" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G90" t="str">
+        <v>4 vs 4</v>
+      </c>
+      <c r="H90">
+        <v>6</v>
+      </c>
+      <c r="I90">
+        <v>6</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>settings/assignment-rules</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="str">
+        <v>3 vs 3</v>
+      </c>
+      <c r="E91" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F91" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G91" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H91">
+        <v>4</v>
+      </c>
+      <c r="I91">
+        <v>4</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>settings/sources</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="E92" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F92" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G92" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>settings/templates</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93">
+        <v>4</v>
+      </c>
+      <c r="D93" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E93" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F93" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H93">
+        <v>4</v>
+      </c>
+      <c r="I93">
+        <v>4</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>settings/whatsapp-numbers</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="E94" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F94" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G94" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H94">
+        <v>2</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>settings/workflow-config</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="str">
+        <v>5 vs 5</v>
+      </c>
+      <c r="E95" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F95" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G95" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H95">
+        <v>6</v>
+      </c>
+      <c r="I95">
+        <v>6</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>settings/workflows</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E96" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F96" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G96" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sms-campaign</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E97" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F97" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G97" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>sources</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="str">
+        <v>0 vs 2</v>
+      </c>
+      <c r="E98" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F98" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G98" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98">
+        <v>5</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>status</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="str">
+        <v>0 vs 3</v>
+      </c>
+      <c r="E99" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F99" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G99" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H99">
+        <v>2</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>templates</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E100" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F100" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="G100" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H100">
+        <v>3</v>
+      </c>
+      <c r="I100">
+        <v>7</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>tqm-metrics</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E101" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F101" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G101" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>types</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E102" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F102" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="G102" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H102">
+        <v>2</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>voice-agents</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E103" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F103" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2 vs 2</v>
+      </c>
+      <c r="H103">
+        <v>3</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>voice-broadcast</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E104" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F104" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G104" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="H104">
+        <v>2</v>
+      </c>
+      <c r="I104">
+        <v>3</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>whatsapp-campaign</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E105" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F105" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G105" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H105">
+        <v>2</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Fully merged</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>whatsapp-personal</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E106" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="F106" t="str">
+        <v>1 vs 0</v>
+      </c>
+      <c r="G106" t="str">
+        <v>7 vs 0</v>
+      </c>
+      <c r="H106">
+        <v>8</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106" t="str">
+        <v>main only</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>workflow-config</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="str">
+        <v>0 vs 5</v>
+      </c>
+      <c r="E107" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F107" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G107" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>8</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>workflows</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="E108" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="F108" t="str">
+        <v>1 vs 1</v>
+      </c>
+      <c r="G108" t="str">
+        <v>0 vs 0</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+      <c r="I108">
+        <v>3</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Partially merged</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L42"/>
   <cols>
-    <col min="1" max="1" width="41.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="65.83203125" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13164,3460 +16606,2747 @@
         <v>Sub-Module</v>
       </c>
       <c r="B1" t="str">
-        <v>Pages (main)</v>
+        <v>What It Does (Business)</v>
       </c>
       <c r="C1" t="str">
-        <v>Pages (omm-dev)</v>
+        <v>User Flow</v>
       </c>
       <c r="D1" t="str">
-        <v>Components</v>
+        <v>Database Tables</v>
       </c>
       <c r="E1" t="str">
-        <v>Services</v>
+        <v>Service File</v>
       </c>
       <c r="F1" t="str">
-        <v>Hooks</v>
+        <v>Hook File</v>
       </c>
       <c r="G1" t="str">
         <v>API Routes</v>
       </c>
       <c r="H1" t="str">
-        <v>Total (main)</v>
+        <v>Status</v>
       </c>
       <c r="I1" t="str">
-        <v>Total (omm-dev)</v>
+        <v>What Developer Must Do</v>
       </c>
       <c r="J1" t="str">
-        <v>Status</v>
+        <v>Architecture Pattern</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Est. Complexity</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>actions</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
+        <v>Dashboard</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Central overview for admission managers. Shows total leads, new leads, conversions, pending follow-ups, funnel visualization (leads per stage), hot leads list, and daily briefing banner. Counselor performance summary and source ROI at a glance.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>User opens /admission/dashboard -&gt; sees KPI cards (total, new, converted, pending follow-ups) -&gt; funnel chart shows leads by stage -&gt; hot leads table -&gt; daily briefing popup if unread -&gt; can filter by institution (super_admin).</v>
       </c>
       <c r="D2" t="str">
-        <v>4 vs 4</v>
+        <v>admission_leads, admission_counselors, admission_lead_stage_history, admission_daily_briefings</v>
       </c>
       <c r="E2" t="str">
-        <v>0 vs 0</v>
+        <v>lead-service.ts (getDashboardSummary, getFunnelSummary)</v>
       </c>
       <c r="F2" t="str">
-        <v>0 vs 0</v>
+        <v>index.ts (useAdmissionDashboard, useDashboardSummary, useFunnelSummary, useFunnelAnalyticsDashboard), use-briefing-notifications.ts</v>
       </c>
       <c r="G2" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>app/api/admission/leads/route.ts, app/api/b2a/admission/stats/route.ts</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Dashboard is functional. Hooks call services directly (not via API). For B2A: create /api/admission/dashboard/route.ts, update hooks to use fetch() instead of direct service calls.</v>
       </c>
       <c r="J2" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>P0</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>activities</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+        <v>Leads Management</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Core CRM module. CRUD for admission leads with 61-column data model. Pipeline/Kanban board, list view, lead detail with tabs (profile, timeline, activities, communication, documents). Stage tracking through 20+ funnel stages. Scoring, hot lead flagging, counselor assignment, follow-up scheduling.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>User opens /admission/leads -&gt; lead list with filters -&gt; Kanban board view -&gt; click lead for detail (/leads/[id]) -&gt; tabs: Overview, Activities, Communication, Documents -&gt; change stage, assign counselor, schedule follow-up, mark hot/priority, add tags -&gt; create from /leads/new.</v>
       </c>
       <c r="D3" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (61 cols), admission_lead_activities (9 cols), admission_lead_stage_history, admission_lead_scores, admission_counselors</v>
       </c>
       <c r="E3" t="str">
-        <v>1 vs 1</v>
+        <v>lead-service.ts, activity-service.ts, lead-scoring-engine-service.ts</v>
       </c>
       <c r="F3" t="str">
-        <v>1 vs 1</v>
+        <v>index.ts (useAdmissionLeads, useAdmissionLead, useLeadMutations, useLeadTimeline, useLeadCommunicationHistory, useFunnelHistory), use-activities.ts, use-lead-scoring.ts</v>
       </c>
       <c r="G3" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+        <v>app/api/admission/leads/route.ts, app/api/b2a/admission/route.ts, app/api/b2a/admission/[id]/route.ts</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Core functionality works. Hooks call LeadService directly. For B2A: move all service calls behind /api/admission/leads/* routes with withAuth(). Missing dedicated routes for: updateStage, toggleHotLead, assignCounselor, scheduleFollowup, addTag, removeTag, single-lead CRUD (/leads/[id]).</v>
       </c>
       <c r="J3" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K3" t="str">
+        <v>P0</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>agentic-query</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>Applications</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Track student applications created from leads. Status workflow (draft -&gt; submitted -&gt; under_review -&gt; approved/rejected -&gt; offer_sent -&gt; enrolled). Application detail with documents.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>User opens /admission/applications -&gt; application list with status filters -&gt; create from lead -&gt; click for detail (/applications/[id]) -&gt; update status, review documents, approve/reject.</v>
       </c>
       <c r="D4" t="str">
-        <v>4 vs 4</v>
+        <v>admission_applications, admission_leads</v>
       </c>
       <c r="E4" t="str">
-        <v>1 vs 1</v>
+        <v>application-service.ts</v>
       </c>
       <c r="F4" t="str">
-        <v>1 vs 1</v>
+        <v>index.ts (useAdmissionApplications, useAdmissionApplication, useApplicationMutations)</v>
       </c>
       <c r="G4" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4">
-        <v>6</v>
+        <v>None dedicated (uses b2a routes)</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Service and hooks exist. Missing dedicated API routes: create /api/admission/applications/route.ts (GET, POST), /[id]/route.ts (GET, PUT, DELETE), /[id]/status/route.ts (PATCH). Hooks call ApplicationService directly.</v>
       </c>
       <c r="J4" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K4" t="str">
+        <v>P0</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ai-responses</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>Counselors</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Manage admission counselors. Sub-pages: daily-view (today's workload), calls (initiate/log calls), reminders (follow-up management), alerts (configurable alert rules), briefing (AI daily summary). Performance tracking.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Main page: counselor list with stats -&gt; /daily-view: today's leads/follow-ups -&gt; /calls: call logs, initiate calls -&gt; /reminders: upcoming follow-ups -&gt; /alerts: alert rule config -&gt; /briefing: AI daily briefing.</v>
       </c>
       <c r="D5" t="str">
-        <v>0 vs 0</v>
+        <v>admission_counselors, admission_leads, admission_lead_activities, admission_daily_briefings</v>
       </c>
       <c r="E5" t="str">
-        <v>2 vs 2</v>
+        <v>counselor-daily-view-service.ts, daily-briefing-service.ts, briefing-delivery-service.ts, activity-alert-service.ts, reminders-service.ts</v>
       </c>
       <c r="F5" t="str">
-        <v>1 vs 1</v>
+        <v>use-counselor-daily-view.ts, use-counselor-performance.ts, use-call-logs.ts, use-call-mutations.ts, use-call-stats.ts, use-reminders.ts, use-activity-alerts.ts, use-briefing-notifications.ts, use-daily-briefing.ts</v>
       </c>
       <c r="G5" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
+        <v>app/api/admission/calls/* (4 routes), app/api/admission/alerts/route.ts</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I5" t="str">
+        <v>All sub-pages have hooks connected. API routes exist for calls and alerts. Missing: counselor CRUD routes, daily-view route, briefing routes. Migrate remaining direct service calls to API routes.</v>
       </c>
       <c r="J5" t="str">
-        <v>Fully merged</v>
+        <v>Mixed: Calls have API routes, others Direct Service</v>
+      </c>
+      <c r="K5" t="str">
+        <v>P0</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ai-suggested-responses</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>Consultants (Education Agents)</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Manage education consultants/agents. Track commissions, referrals, payouts, rewards, analytics. 57-column consultant model. Bulk CSV import.</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Main page: consultant list -&gt; /new: create -&gt; /[id]: detail -&gt; /[id]/edit: edit -&gt; Sub-pages: /commissions, /referrals, /payouts, /rewards, /analytics. Import via CSV template.</v>
       </c>
       <c r="D6" t="str">
-        <v>1 vs 1</v>
+        <v>education_consultants (57 cols), admission_leads</v>
       </c>
       <c r="E6" t="str">
-        <v>0 vs 0</v>
+        <v>consultant-service.ts</v>
       </c>
       <c r="F6" t="str">
-        <v>0 vs 0</v>
+        <v>use-consultants.ts</v>
       </c>
       <c r="G6" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
+        <v>app/api/admission/consultants/import/route.ts, /template/route.ts</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Service and hooks fully wired. Import/template routes exist. Missing: CRUD routes (/api/admission/consultants/route.ts, /[id]/route.ts), commission routes, payout routes, rewards routes. Hooks call service directly.</v>
       </c>
       <c r="J6" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K6" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>alerts</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>Marketing &gt; Campaigns</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Monitor SMS and WhatsApp campaigns. Campaign stats, delivery metrics, active sequences, execution logs, real-time updates, ROI tracking, audience segments.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Open /campaigns/monitoring -&gt; overview cards -&gt; delivery charts -&gt; active sequences -&gt; execution logs. /campaigns/roi -&gt; ROI analytics. /campaigns/segments -&gt; audience management.</v>
       </c>
       <c r="D7" t="str">
-        <v>0 vs 0</v>
+        <v>admission_campaign_logs, admission_campaign_queue, admission_sms_logs, admission_whatsapp_logs, admission_drip_sequences, admission_drip_schedule</v>
       </c>
       <c r="E7" t="str">
-        <v>1 vs 1</v>
+        <v>campaign-monitoring-service.ts, campaign-processor-service.ts, campaign-roi-service.ts, sms-campaign-service.ts, whatsapp-campaign-service.ts, drip-executor-service.ts, communication-cost-service.ts</v>
       </c>
       <c r="F7" t="str">
-        <v>1 vs 1</v>
+        <v>use-campaign-monitoring.ts, use-campaign-processor.ts, use-campaign-roi.ts, use-sms-campaign.ts, use-whatsapp-campaign.ts, use-drip-executor.ts, use-communication-costs.ts</v>
       </c>
       <c r="G7" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
+        <v>app/api/admission/campaigns/roi/route.ts, /segments/* (4 routes), app/api/admission/costs/route.ts</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Rich services and hooks. ROI and segments have API routes. Missing: campaign monitoring dashboard route, campaign CRUD routes.</v>
       </c>
       <c r="J7" t="str">
-        <v>Fully merged</v>
+        <v>Mixed: Some API routes, others Direct Service</v>
+      </c>
+      <c r="K7" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>analytics</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+        <v>Marketing &gt; WhatsApp Chat</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Two-way WhatsApp messaging. Real-time chat with leads, conversation management (assign, resolve, reopen), document sharing, quick replies, performance analytics, settings.</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Open /chat -&gt; conversation list sidebar -&gt; select to chat -&gt; send messages, share docs, quick replies -&gt; /chat/performance: response times -&gt; /chat/settings: config.</v>
       </c>
       <c r="D8" t="str">
-        <v>0 vs 0</v>
+        <v>admission_whatsapp_logs, admission_communication_templates, admission_leads, admission_counselors</v>
       </c>
       <c r="E8" t="str">
-        <v>0 vs 0</v>
+        <v>whatsapp-campaign-service.ts, communication-templates-service.ts</v>
       </c>
       <c r="F8" t="str">
-        <v>0 vs 0</v>
+        <v>use-chat-realtime.ts, use-chat-stats.ts, use-chat-mutations.ts, use-conversation.ts, use-conversations.ts, use-quick-replies.ts, use-wa-consent.ts, use-wa-document-catalog.ts, use-wa-segments.ts, use-wa-settings.ts</v>
       </c>
       <c r="G8" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
+        <v>13+ routes: /chat/conversations/*, /chat/consent/*, /chat/documents/*, /chat/quick-replies, /chat/stats, /chat/templates/*, /chat/counselor-performance</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I8" t="str">
+        <v>MOST COMPLETE sub-module. 13+ API routes, extensive hooks. All wired. For improvement: verify withAuth() on all routes, test real-time subscriptions.</v>
       </c>
       <c r="J8" t="str">
-        <v>Fully merged</v>
+        <v>API Route Pattern (most mature)</v>
+      </c>
+      <c r="K8" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>applications</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
+        <v>Marketing &gt; Chatbot</v>
+      </c>
+      <c r="B9" t="str">
+        <v>AI chatbot for automated lead engagement. Configure behavior, manage knowledge base (FAQs, docs), analytics (sessions, resolution rate), human handoff.</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Open /chatbot -&gt; config + analytics overview -&gt; /chatbot/knowledge: FAQ management -&gt; /chatbot/analytics: metrics -&gt; view sessions, hand off to human.</v>
       </c>
       <c r="D9" t="str">
-        <v>3 vs 3</v>
+        <v>chatbot_sessions, chatbot_knowledge (custom tables)</v>
       </c>
       <c r="E9" t="str">
-        <v>1 vs 1</v>
+        <v>admission-ai-service.ts, ai-response-service.ts</v>
       </c>
       <c r="F9" t="str">
-        <v>0 vs 0</v>
+        <v>use-chatbot-config.ts, use-chatbot-analytics.ts, use-chatbot-knowledge.ts, use-chatbot-sessions.ts</v>
       </c>
       <c r="G9" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
+        <v>6 routes: /chatbot/config, /analytics, /knowledge, /sessions, /sessions/[id], /sessions/[id]/handoff</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Fully wired with API routes. Verify: knowledge base table exists, AI integration works, handoff workflow end-to-end.</v>
       </c>
       <c r="J9" t="str">
-        <v>Fully merged</v>
+        <v>API Route Pattern</v>
+      </c>
+      <c r="K9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>apply</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
+        <v>Marketing &gt; Parent Comm.</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Outreach to parents/guardians. Send personalized messages about admission status, open house invitations, scholarships. Track parent engagement.</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Open /parent-communication -&gt; parent contact list -&gt; compose messages -&gt; view delivery status -&gt; engagement metrics.</v>
       </c>
       <c r="D10" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (parent fields), admission_sms_logs, admission_whatsapp_logs</v>
       </c>
       <c r="E10" t="str">
-        <v>0 vs 0</v>
+        <v>parent-communication-service.ts</v>
       </c>
       <c r="F10" t="str">
-        <v>0 vs 0</v>
+        <v>use-parent-communication.ts</v>
       </c>
       <c r="G10" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Service and hooks exist, page wired. MISSING: API routes (/api/admission/parent-communication/route.ts). Create routes with withAuth(), migrate hooks from direct service calls.</v>
       </c>
       <c r="J10" t="str">
-        <v>omm-dev only</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K10" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>assignment-rules</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+        <v>Marketing &gt; Re-engagement</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Re-engage cold/dormant leads. Identify inactive leads, create re-engagement campaigns, track success, mark leads as hot again.</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Open /re-engagement -&gt; dormant leads list -&gt; filter by days inactive, stage -&gt; select for campaign -&gt; send bulk messages -&gt; track response.</v>
       </c>
       <c r="D11" t="str">
-        <v>0 vs 3</v>
+        <v>admission_leads, admission_sms_logs, admission_whatsapp_logs</v>
       </c>
       <c r="E11" t="str">
-        <v>1 vs 1</v>
+        <v>re-engagement-service.ts</v>
       </c>
       <c r="F11" t="str">
-        <v>1 vs 1</v>
+        <v>use-re-engagement.ts</v>
       </c>
       <c r="G11" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
+        <v>None</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Service and hooks exist. MISSING: API routes. Create /api/admission/re-engagement/route.ts. Migrate hook calls from direct service.</v>
       </c>
       <c r="J11" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K11" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>b2a-bridge</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
+        <v>Marketing &gt; Voice Agents</v>
+      </c>
+      <c r="B12" t="str">
+        <v>AI voice calling agents. Configure AI personas, initiate automated calls, track outcomes. Supports outbound follow-up, inquiry response, appointment scheduling.</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Open /voice-agents -&gt; agent configs list -&gt; create/edit configs -&gt; view call history -&gt; call analytics.</v>
       </c>
       <c r="D12" t="str">
-        <v>0 vs 0</v>
+        <v>voice_agent_configs, voice_agent_calls (custom tables)</v>
       </c>
       <c r="E12" t="str">
-        <v>0 vs 0</v>
+        <v>lib/services/ai/voice-agent-service.ts</v>
       </c>
       <c r="F12" t="str">
-        <v>0 vs 0</v>
+        <v>use-voice-agents.ts</v>
       </c>
       <c r="G12" t="str">
-        <v>3 vs 3</v>
-      </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-      <c r="I12">
-        <v>3</v>
+        <v>app/api/admission/voice-agents/route.ts, /calls/route.ts</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Service, hooks, API routes exist. REQUIRES: external voice provider (Twilio/Bland.ai). Verify DB tables exist, provider credentials configured.</v>
       </c>
       <c r="J12" t="str">
-        <v>Fully merged</v>
+        <v>API Route Pattern (service in /ai/)</v>
+      </c>
+      <c r="K12" t="str">
+        <v>P3</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>bridge</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
+        <v>Marketing &gt; Voice Broadcast</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bulk voice message broadcasting. Create pre-recorded or TTS messages, define audience, schedule broadcasts, track delivery.</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Open /voice-broadcast -&gt; campaign list -&gt; create (select audience, upload message, schedule) -&gt; delivery stats.</v>
       </c>
       <c r="D13" t="str">
-        <v>0 vs 0</v>
+        <v>voice_broadcasts, voice_broadcast_logs (custom tables)</v>
       </c>
       <c r="E13" t="str">
-        <v>0 vs 0</v>
+        <v>lib/services/telephony/voice-broadcast-service.ts</v>
       </c>
       <c r="F13" t="str">
-        <v>0 vs 0</v>
+        <v>use-voice-broadcast.ts</v>
       </c>
       <c r="G13" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
+        <v>app/api/admission/voice-broadcast/route.ts</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Service, hooks, API route exist. REQUIRES: telephony provider. Verify DB tables exist, provider credentials configured.</v>
       </c>
       <c r="J13" t="str">
-        <v>Fully merged</v>
+        <v>API Route Pattern (service in /telephony/)</v>
+      </c>
+      <c r="K13" t="str">
+        <v>P3</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>briefing</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
+        <v>Marketing &gt; Publishers</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Track education publishers/agents. View performance (leads, conversions), manage profiles. Reuses ConsultantService since publishers are a consultant type.</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Open /publishers -&gt; publisher list with performance -&gt; add/edit -&gt; referral details -&gt; commissions.</v>
       </c>
       <c r="D14" t="str">
-        <v>0 vs 0</v>
+        <v>education_consultants (publishers = subset), admission_leads</v>
       </c>
       <c r="E14" t="str">
-        <v>2 vs 2</v>
+        <v>consultant-service.ts (shared)</v>
       </c>
       <c r="F14" t="str">
-        <v>2 vs 2</v>
+        <v>use-consultants.ts (shared)</v>
       </c>
       <c r="G14" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
+        <v>app/api/admission/consultants/* (shared)</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Reuses Consultant infrastructure. Data table calls ConsultantService directly. Consider: add publisher-specific type/filter field.</v>
       </c>
       <c r="J14" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call, shares Consultant</v>
+      </c>
+      <c r="K14" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>briefing-notification-banner</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
+        <v>Data Quality &gt; Phone Valid.</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Validate phone numbers. Detect invalid formats, missing codes, duplicates. Validation stats, issue breakdown, bulk fix.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Open /phone-validation -&gt; stats cards -&gt; issue breakdown chart -&gt; invalid phones table -&gt; batch-fix -&gt; export.</v>
       </c>
       <c r="D15" t="str">
-        <v>1 vs 1</v>
+        <v>admission_leads (phone, alternate_phone)</v>
       </c>
       <c r="E15" t="str">
-        <v>0 vs 0</v>
+        <v>data-quality-service.ts</v>
       </c>
       <c r="F15" t="str">
-        <v>0 vs 0</v>
+        <v>use-data-quality.ts (usePhoneValidationStats, useInvalidPhones, usePhoneIssueBreakdown)</v>
       </c>
       <c r="G15" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Service and hooks exist and page uses them. MISSING: API routes (/api/admission/data-quality/phone-validation/route.ts).</v>
       </c>
       <c r="J15" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K15" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>briefing-popup</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
+        <v>Data Quality &gt; Deduplication</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Detect and merge duplicate leads. Scan based on phone, email, name similarity. Merge with field-by-field conflict resolution.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Open /deduplication -&gt; Scan for Duplicates -&gt; duplicate groups -&gt; select group -&gt; choose master -&gt; merge.</v>
       </c>
       <c r="D16" t="str">
-        <v>1 vs 1</v>
+        <v>admission_leads</v>
       </c>
       <c r="E16" t="str">
-        <v>0 vs 0</v>
+        <v>data-quality-service.ts</v>
       </c>
       <c r="F16" t="str">
-        <v>0 vs 0</v>
+        <v>use-data-quality.ts (useDuplicateGroups, useMergeMutations)</v>
       </c>
       <c r="G16" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Service and hooks exist. MISSING: API routes for scan, groups, merge. Ensure merge is transactional.</v>
       </c>
       <c r="J16" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K16" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>calls</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
+        <v>Data Quality &gt; Data Profiling</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Analyze lead data completeness and quality. Field-level fill rates, data quality scores, recommendations.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Open /data-profiling -&gt; overall quality score -&gt; field completeness chart -&gt; issues by severity -&gt; export.</v>
       </c>
       <c r="D17" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads</v>
       </c>
       <c r="E17" t="str">
-        <v>0 vs 0</v>
+        <v>data-quality-service.ts</v>
       </c>
       <c r="F17" t="str">
-        <v>3 vs 3</v>
+        <v>use-data-quality.ts (useDataProfilingMetrics, useFieldAnalysis, useDataIssues)</v>
       </c>
       <c r="G17" t="str">
-        <v>4 vs 4</v>
-      </c>
-      <c r="H17">
-        <v>7</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
+        <v>None</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Service and hooks exist, page uses them (confirmed). MISSING: API routes.</v>
       </c>
       <c r="J17" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K17" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>campaign-monitoring</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
+        <v>Settings &gt; General</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Module-level settings hub. Navigation page linking to sub-settings (assignment rules, sources, templates, workflows, whatsapp numbers, workflow config).</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Open /settings -&gt; settings categories as cards/links -&gt; navigate to sub-settings.</v>
       </c>
       <c r="D18" t="str">
-        <v>5 vs 5</v>
+        <v>No dedicated table</v>
       </c>
       <c r="E18" t="str">
-        <v>0 vs 0</v>
+        <v>None</v>
       </c>
       <c r="F18" t="str">
-        <v>0 vs 0</v>
+        <v>Uses useAuth, useUserInstitutionAccess</v>
       </c>
       <c r="G18" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H18">
-        <v>5</v>
-      </c>
-      <c r="I18">
-        <v>5</v>
+        <v>None</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Page Only</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Navigation hub - no dedicated backend needed. Consider: create admission_settings table and /api/admission/settings/route.ts for module config.</v>
       </c>
       <c r="J18" t="str">
-        <v>Fully merged</v>
+        <v>Navigation page</v>
+      </c>
+      <c r="K18" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>campaigns</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
+        <v>Settings &gt; Workflows</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Automated workflows triggered by lead events. Define triggers, conditions, actions. Workflow execution tracking.</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Open /settings/workflows -&gt; workflow list -&gt; create with trigger-condition-action builder -&gt; enable/disable -&gt; execution history.</v>
       </c>
       <c r="D19" t="str">
-        <v>0 vs 0</v>
+        <v>admission_workflows, admission_workflow_executions</v>
       </c>
       <c r="E19" t="str">
-        <v>4 vs 4</v>
+        <v>workflows-service.ts</v>
       </c>
       <c r="F19" t="str">
-        <v>5 vs 5</v>
+        <v>use-workflows.ts</v>
       </c>
       <c r="G19" t="str">
-        <v>5 vs 5</v>
-      </c>
-      <c r="H19">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>18</v>
+        <v>None</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Service and hooks fully wired. MISSING: API routes. Create /api/admission/settings/workflows/route.ts and /[id]/route.ts.</v>
       </c>
       <c r="J19" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K19" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>chat</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
+        <v>Settings &gt; Assignment Rules</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Auto lead-to-counselor assignment. Rules based on source, program, location, score. Round-robin, weighted, load-balanced.</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Open /settings/assignment-rules -&gt; rule list -&gt; create rule -&gt; set criteria/distribution -&gt; enable/disable/reorder.</v>
       </c>
       <c r="D20" t="str">
-        <v>0 vs 3</v>
+        <v>admission_assignment_rules</v>
       </c>
       <c r="E20" t="str">
-        <v>0 vs 0</v>
+        <v>assignment-rules-service.ts</v>
       </c>
       <c r="F20" t="str">
-        <v>8 vs 8</v>
+        <v>use-assignment-rules.ts</v>
       </c>
       <c r="G20" t="str">
-        <v>15 vs 18</v>
-      </c>
-      <c r="H20">
-        <v>23</v>
-      </c>
-      <c r="I20">
-        <v>32</v>
+        <v>None</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Service and hooks wired. Data table and row actions use hooks. MISSING: API routes.</v>
       </c>
       <c r="J20" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K20" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>chatbot</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
+        <v>Settings &gt; Scoring Rules</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Lead scoring criteria config. Define rules by demographics, engagement, qualification. Weighted scoring with auto-recalculation.</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Open /scoring-rules -&gt; rules table -&gt; create/edit -&gt; set category, criteria, points -&gt; enable/disable.</v>
       </c>
       <c r="D21" t="str">
-        <v>0 vs 0</v>
+        <v>admission_scoring_rules, admission_lead_scores</v>
       </c>
       <c r="E21" t="str">
-        <v>0 vs 0</v>
+        <v>scoring-rules-service.ts, lead-scoring-engine-service.ts</v>
       </c>
       <c r="F21" t="str">
-        <v>4 vs 4</v>
+        <v>use-scoring-rules.ts, use-lead-scoring.ts</v>
       </c>
       <c r="G21" t="str">
-        <v>6 vs 6</v>
-      </c>
-      <c r="H21">
-        <v>10</v>
-      </c>
-      <c r="I21">
-        <v>13</v>
+        <v>None</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Service and hooks wired. Data table uses service directly. MISSING: API routes.</v>
       </c>
       <c r="J21" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K21" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>communication</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
+        <v>Settings &gt; Sources</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Track lead sources (website, walk-in, referral, social). Source performance metrics, conversion rates, ROI.</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Open /settings/sources -&gt; source performance table -&gt; add custom sources -&gt; source analytics.</v>
       </c>
       <c r="D22" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (source column aggregation)</v>
       </c>
       <c r="E22" t="str">
-        <v>1 vs 1</v>
+        <v>source-tracking-service.ts</v>
       </c>
       <c r="F22" t="str">
-        <v>1 vs 1</v>
+        <v>use-data-quality.ts (useSourceTracking), use-consultants.ts (useSourcePerformance)</v>
       </c>
       <c r="G22" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
+        <v>None</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Service and hooks wired. Data table uses service directly. MISSING: API routes.</v>
       </c>
       <c r="J22" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K22" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>consultants</v>
-      </c>
-      <c r="B23">
-        <v>8</v>
-      </c>
-      <c r="C23">
-        <v>8</v>
+        <v>Settings &gt; Templates</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Communication templates for SMS, Email, WhatsApp. Variable placeholders, template analytics, email builder, document templates.</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Open /settings/templates -&gt; template list by channel -&gt; create/edit with variables -&gt; /analytics -&gt; /email-builder -&gt; /documents.</v>
       </c>
       <c r="D23" t="str">
-        <v>6 vs 6</v>
+        <v>admission_communication_templates</v>
       </c>
       <c r="E23" t="str">
-        <v>1 vs 1</v>
+        <v>communication-templates-service.ts</v>
       </c>
       <c r="F23" t="str">
-        <v>2 vs 1</v>
+        <v>use-communication-templates.ts, use-template-analytics.ts</v>
       </c>
       <c r="G23" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="H23">
-        <v>19</v>
-      </c>
-      <c r="I23">
-        <v>18</v>
+        <v>/chat/templates/analytics, /chat/templates/refresh-quality (WhatsApp-specific)</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Service and hooks wired. Template quality routes exist (WA-specific). MISSING: CRUD routes for templates.</v>
       </c>
       <c r="J23" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K23" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>core</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
+        <v>Settings &gt; WhatsApp Numbers</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Manage WhatsApp Business API numbers. Add/remove numbers, set primary, configure settings.</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Open /settings/whatsapp-numbers -&gt; registered numbers -&gt; add new -&gt; set primary -&gt; configure.</v>
       </c>
       <c r="D24" t="str">
-        <v>0 vs 0</v>
+        <v>WhatsApp number config table</v>
       </c>
       <c r="E24" t="str">
-        <v>1 vs 2</v>
+        <v>Handled by API routes directly</v>
       </c>
       <c r="F24" t="str">
-        <v>0 vs 0</v>
+        <v>Page uses useAuth</v>
       </c>
       <c r="G24" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>2</v>
+        <v>3 routes: /settings/whatsapp-numbers/route.ts, /[id]/route.ts, /[id]/primary/route.ts, /settings/whatsapp/route.ts</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I24" t="str">
+        <v>API routes are comprehensive (CRUD + set primary). Well-structured. Verify: withAuth() on all routes.</v>
       </c>
       <c r="J24" t="str">
-        <v>Partially merged</v>
+        <v>API Route Pattern</v>
+      </c>
+      <c r="K24" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>core-layout</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
+        <v>Settings &gt; Workflow Config</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Workflow engine configuration. Custom stage transitions, stage-specific actions, notification rules.</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Open /settings/workflow-config -&gt; stage transition rules -&gt; allowed transitions -&gt; automated actions.</v>
       </c>
       <c r="D25" t="str">
-        <v>0 vs 0</v>
+        <v>admission_workflow_configs</v>
       </c>
       <c r="E25" t="str">
-        <v>0 vs 0</v>
+        <v>workflow-config-service.ts</v>
       </c>
       <c r="F25" t="str">
-        <v>0 vs 0</v>
+        <v>use-workflow-config.ts</v>
       </c>
       <c r="G25" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H25">
-        <v>2</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
+        <v>None</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Service and hooks wired. MISSING: API routes.</v>
       </c>
       <c r="J25" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K25" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>costs</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
+        <v>AI Insights</v>
+      </c>
+      <c r="B26" t="str">
+        <v>AI-powered analytics. Trend detection, anomaly alerts, actionable recommendations. Insight actions (execute suggested fixes). Priority-based dismissal.</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Open /insights -&gt; insight cards by priority -&gt; filter by type -&gt; click for details/actions -&gt; dismiss -&gt; /insights/status: pipeline health.</v>
       </c>
       <c r="D26" t="str">
-        <v>0 vs 0</v>
+        <v>admission_ai_insights, admission_action_executions, admission_leads</v>
       </c>
       <c r="E26" t="str">
-        <v>0 vs 0</v>
+        <v>ai-insights-service.ts, insight-actions-service.ts, admission-ai-service.ts</v>
       </c>
       <c r="F26" t="str">
-        <v>0 vs 0</v>
+        <v>use-ai-insights.ts, use-insight-actions.ts</v>
       </c>
       <c r="G26" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
+        <v>app/api/admission/insights/generate/route.ts</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Service and hooks wired. Generation route exists. MISSING: insight CRUD routes (list, dismiss). Needs OpenAI/Anthropic API key.</v>
       </c>
       <c r="J26" t="str">
-        <v>Fully merged</v>
+        <v>Mixed: generation via API, reading via Direct Service</v>
+      </c>
+      <c r="K26" t="str">
+        <v>P3</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>counselors</v>
-      </c>
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27">
-        <v>6</v>
+        <v>Analytics</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Admission analytics dashboard. Enhanced funnel (avg days/stage, stuck leads, drop-off, bottlenecks), source ROI, counselor benchmarking, WoW trends.</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Open /analytics -&gt; enhanced funnel viz -&gt; drop-off analysis -&gt; stuck leads table -&gt; bottleneck alerts -&gt; source comparison -&gt; counselor ranking.</v>
       </c>
       <c r="D27" t="str">
-        <v>7 vs 7</v>
+        <v>admission_leads, admission_lead_stage_history, admission_counselors</v>
       </c>
       <c r="E27" t="str">
-        <v>1 vs 1</v>
+        <v>lead-service.ts (getFunnelSummary, getDashboardSummary)</v>
       </c>
       <c r="F27" t="str">
-        <v>2 vs 2</v>
+        <v>index.ts (useFunnelAnalyticsDashboard, useCounselorPerformance, useSourceROI)</v>
       </c>
       <c r="G27" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H27">
-        <v>16</v>
-      </c>
-      <c r="I27">
-        <v>16</v>
+        <v>None</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Complex inline aggregation in hooks (~100 lines). Page is wired. MISSING: API routes. Move aggregation to analytics service and /api/admission/analytics/route.ts.</v>
       </c>
       <c r="J27" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call with heavy inline logic</v>
+      </c>
+      <c r="K27" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>dashboard</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
+        <v>Group Dashboard</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Multi-institution admission overview. Compare performance across institutions, aggregate funnel, counselor metrics.</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Open /group-dashboard -&gt; institution comparison cards -&gt; aggregate funnel -&gt; per-institution stats -&gt; drill down.</v>
       </c>
       <c r="D28" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (cross-institution), institutions</v>
       </c>
       <c r="E28" t="str">
-        <v>0 vs 0</v>
+        <v>group-dashboard-service.ts</v>
       </c>
       <c r="F28" t="str">
-        <v>0 vs 0</v>
+        <v>use-group-dashboard.ts</v>
       </c>
       <c r="G28" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Service and hooks exist. MISSING: API routes (/api/admission/group-dashboard/route.ts). Needs super_admin access check.</v>
       </c>
       <c r="J28" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K28" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>data-profiling</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
+        <v>Selection &gt; GD-PI</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Group Discussion &amp; Personal Interview. Create sessions, add candidates, assign evaluators, score on criteria, auto-rank, generate results.</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Open /gd-pi -&gt; session list -&gt; create (name, date, evaluators) -&gt; add candidates -&gt; score during session -&gt; auto-rank -&gt; results -&gt; link to merit list.</v>
       </c>
       <c r="D29" t="str">
-        <v>0 vs 0</v>
+        <v>admission_gdpi_sessions, admission_gdpi_candidates, admission_gdpi_evaluators, admission_gdpi_scores</v>
       </c>
       <c r="E29" t="str">
-        <v>0 vs 0</v>
+        <v>gdpi-service.ts</v>
       </c>
       <c r="F29" t="str">
-        <v>0 vs 0</v>
+        <v>use-gdpi.ts</v>
       </c>
       <c r="G29" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
+        <v>4 routes: /gdpi/route.ts, /[id]/route.ts, /[id]/candidates/route.ts, /[id]/scores/route.ts</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Fully wired. API routes are comprehensive. Hooks call service directly (not API yet). For B2A: migrate hooks to fetch API routes.</v>
       </c>
       <c r="J29" t="str">
-        <v>omm-dev only</v>
+        <v>Direct Service + API routes exist (not yet connected)</v>
+      </c>
+      <c r="K29" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>data-quality</v>
-      </c>
-      <c r="B30">
-        <v>3</v>
-      </c>
-      <c r="C30">
-        <v>3</v>
+        <v>Selection &gt; Screening Exam</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Entrance exam management. Create schedules, assign candidates, manage venues, record scores, result reports.</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Open /screening-exam -&gt; exam list -&gt; create -&gt; assign candidates -&gt; enter scores -&gt; results.</v>
       </c>
       <c r="D30" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (scores), custom screening tables</v>
       </c>
       <c r="E30" t="str">
-        <v>1 vs 1</v>
+        <v>screening-exam-service.ts</v>
       </c>
       <c r="F30" t="str">
-        <v>1 vs 1</v>
+        <v>use-screening-exams.ts</v>
       </c>
       <c r="G30" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H30">
-        <v>5</v>
-      </c>
-      <c r="I30">
-        <v>5</v>
+        <v>None</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Service and hooks wired to page. MISSING: API routes.</v>
       </c>
       <c r="J30" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K30" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>deduplication</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
+        <v>Selection &gt; Merit List</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Merit-based selection lists. Combine scores from exam, GD-PI, academics. Configure weights. Auto-rank. Category cutoffs.</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Open /merit-list -&gt; config list -&gt; generate (set weights) -&gt; ranked candidates -&gt; publish/unpublish -&gt; export.</v>
       </c>
       <c r="D31" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads (scores), admission_gdpi_scores</v>
       </c>
       <c r="E31" t="str">
-        <v>0 vs 0</v>
+        <v>merit-list-service.ts</v>
       </c>
       <c r="F31" t="str">
-        <v>0 vs 0</v>
+        <v>None (components call service directly)</v>
       </c>
       <c r="G31" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Service exists but NO hook layer. Components call MeritListService directly. CREATE: use-merit-lists.ts hook, /api/admission/merit-list/route.ts. Wire full chain.</v>
       </c>
       <c r="J31" t="str">
-        <v>omm-dev only</v>
+        <v>Direct Component -&gt; Service (no hook)</v>
+      </c>
+      <c r="K31" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>documentation</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
+        <v>Selection &gt; Interviews</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Interview scheduling and management. Create slots, assign interviewers, track outcomes (selected/waitlisted/rejected), record feedback.</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Open /interviews -&gt; schedule -&gt; create slot -&gt; assign candidates -&gt; record outcome/feedback -&gt; analytics.</v>
       </c>
       <c r="D32" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads, custom interview tables</v>
       </c>
       <c r="E32" t="str">
-        <v>0 vs 0</v>
+        <v>interview-service.ts</v>
       </c>
       <c r="F32" t="str">
-        <v>0 vs 0</v>
+        <v>use-interviews.ts</v>
       </c>
       <c r="G32" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H32">
-        <v>6</v>
-      </c>
-      <c r="I32">
-        <v>10</v>
+        <v>None</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Service and hooks wired to page. MISSING: API routes.</v>
       </c>
       <c r="J32" t="str">
-        <v>Partially merged</v>
+        <v>Direct Service Call (pre-B2A)</v>
+      </c>
+      <c r="K32" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>documents</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
+        <v>Financial &gt; Scholarships</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Scholarship management. Types (merit, need, sports, minority), eligibility criteria, applications, disbursements. Detail/edit views.</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Open /scholarships -&gt; list -&gt; create (name, type, criteria, amount) -&gt; view apps -&gt; approve/reject -&gt; /[id]/edit.</v>
       </c>
       <c r="D33" t="str">
-        <v>0 vs 3</v>
+        <v>admission_leads, custom scholarship tables</v>
       </c>
       <c r="E33" t="str">
-        <v>0 vs 1</v>
+        <v>scholarship-service.ts</v>
       </c>
       <c r="F33" t="str">
-        <v>0 vs 0</v>
+        <v>use-data-quality.ts (misplaced: useScholarships, useScholarshipApplications)</v>
       </c>
       <c r="G33" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>5</v>
+        <v>None</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Service and hooks wired but hooks are MISPLACED in use-data-quality.ts. Move to dedicated use-scholarships.ts. MISSING: API routes.</v>
       </c>
       <c r="J33" t="str">
-        <v>omm-dev only</v>
+        <v>Direct Service Call. Hooks misplaced.</v>
+      </c>
+      <c r="K33" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>drip-sequence-status</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
+        <v>Financial &gt; Loans</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Education loan tracking. Loan partners (banks, NBFCs), application stages, amount tracking, EMI calculations.</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Open /loans -&gt; tabs: Applications + Partners -&gt; create/update applications -&gt; manage partners -&gt; track disbursement.</v>
       </c>
       <c r="D34" t="str">
-        <v>1 vs 1</v>
+        <v>admission_loan_applications, admission_loan_partners</v>
       </c>
       <c r="E34" t="str">
-        <v>0 vs 0</v>
+        <v>loan-service.ts</v>
       </c>
       <c r="F34" t="str">
-        <v>0 vs 0</v>
+        <v>use-loans.ts</v>
       </c>
       <c r="G34" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
+        <v>4 routes: /loans/route.ts, /[id]/route.ts, /partners/route.ts, /partners/[id]/route.ts</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Fully wired with comprehensive API routes. Hooks call service directly. For B2A: migrate hooks to use API routes.</v>
       </c>
       <c r="J34" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service + API routes exist</v>
+      </c>
+      <c r="K34" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>echo-bubble</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
+        <v>Financial &gt; Hostels</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Hostel room allocation for admitted students. Manage buildings, rooms, beds. Waitlist management, occupancy tracking.</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Open /hostels -&gt; buildings with occupancy -&gt; rooms with availability -&gt; allocate room -&gt; waitlist -&gt; dashboard.</v>
       </c>
       <c r="D35" t="str">
-        <v>1 vs 1</v>
+        <v>Custom hostel tables (may reference campus-living tables)</v>
       </c>
       <c r="E35" t="str">
-        <v>0 vs 0</v>
+        <v>hostel-service.ts (admission-specific)</v>
       </c>
       <c r="F35" t="str">
-        <v>0 vs 0</v>
+        <v>use-data-quality.ts (misplaced: useHostels, useHostelAllocations, useHostelWaitlist)</v>
       </c>
       <c r="G35" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
+        <v>None</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Service exists. Hooks MISPLACED in use-data-quality.ts. MISSING: API routes. Move hooks to use-hostels.ts. May need integration with campus-living module.</v>
       </c>
       <c r="J35" t="str">
-        <v>Fully merged</v>
+        <v>Direct Service Call. Hooks misplaced.</v>
+      </c>
+      <c r="K35" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>email</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
+        <v>Enrollment &gt; Offer Letters</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Generate/manage admission offer letters. Templates, auto-populate student/program data, send via email/WhatsApp, track acceptance.</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Open /offer-letter -&gt; offer list (draft/sent/accepted/declined) -&gt; generate -&gt; send -&gt; track response.</v>
       </c>
       <c r="D36" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads, custom offer_letters table</v>
       </c>
       <c r="E36" t="str">
-        <v>0 vs 0</v>
+        <v>offer-letter-service.ts</v>
       </c>
       <c r="F36" t="str">
-        <v>0 vs 0</v>
+        <v>use-offer-letters.ts (exists but may be unused by page)</v>
       </c>
       <c r="G36" t="str">
-        <v>3 vs 3</v>
-      </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
-      <c r="I36">
-        <v>3</v>
+        <v>None</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Service exists. Hook file exists. Page delegates to components that call service directly (no hook layer used). MISSING: API routes. Wire page through hooks -&gt; API -&gt; service.</v>
       </c>
       <c r="J36" t="str">
-        <v>Fully merged</v>
+        <v>Component -&gt; Service (hook exists but unused)</v>
+      </c>
+      <c r="K36" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>expos</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
+        <v>Enrollment &gt; Seat Confirm.</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Track seat confirmation payments. Payment status, receipt generation, deadline management.</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Open /seat-confirmation -&gt; confirmation list -&gt; track payments -&gt; mark confirmed/expired -&gt; send reminders.</v>
       </c>
       <c r="D37" t="str">
-        <v>0 vs 0</v>
+        <v>admission_payments, admission_leads</v>
       </c>
       <c r="E37" t="str">
-        <v>1 vs 0</v>
+        <v>seat-confirmation-service.ts</v>
       </c>
       <c r="F37" t="str">
-        <v>1 vs 0</v>
+        <v>use-seat-confirmation.ts (exists)</v>
       </c>
       <c r="G37" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H37">
-        <v>2</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
+        <v>None</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Service and hook file exist. Page components call service directly. MISSING: API routes. Wire through hooks -&gt; API -&gt; service.</v>
       </c>
       <c r="J37" t="str">
-        <v>main only</v>
+        <v>Component -&gt; Service (hook exists but unused)</v>
+      </c>
+      <c r="K37" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>feedback</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
+        <v>Enrollment &gt; Lateral Entry</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Lateral admission (direct 2nd/3rd year entry). Different eligibility, documents, seat matrix.</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Open /lateral-entry -&gt; application list -&gt; add new -&gt; verify documents -&gt; approve/reject -&gt; allocate section.</v>
       </c>
       <c r="D38" t="str">
-        <v>0 vs 3</v>
+        <v>admission_leads, admission_applications (lateral flag)</v>
       </c>
       <c r="E38" t="str">
-        <v>1 vs 1</v>
+        <v>lateral-entry-service.ts</v>
       </c>
       <c r="F38" t="str">
-        <v>1 vs 1</v>
+        <v>use-lateral-entry.ts (exists)</v>
       </c>
       <c r="G38" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H38">
-        <v>2</v>
-      </c>
-      <c r="I38">
-        <v>6</v>
+        <v>None</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Service and hook file exist. Page components call service directly. MISSING: API routes. Wire full chain.</v>
       </c>
       <c r="J38" t="str">
-        <v>Partially merged</v>
+        <v>Component -&gt; Service (hook exists but unused)</v>
+      </c>
+      <c r="K38" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gd-pi</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
+        <v>Enrollment &gt; Documents</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Document verification workflow. Track required docs per student, status (pending/approved/rejected/reupload). Bulk actions.</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Open /documents -&gt; verification table -&gt; filter by status -&gt; review -&gt; approve/reject/request reupload -&gt; bulk actions.</v>
       </c>
       <c r="D39" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads, custom document tables</v>
       </c>
       <c r="E39" t="str">
-        <v>0 vs 1</v>
+        <v>document-service.ts</v>
       </c>
       <c r="F39" t="str">
-        <v>0 vs 1</v>
+        <v>None (components call service directly)</v>
       </c>
       <c r="G39" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>3</v>
+        <v>None (chat/documents routes are for WhatsApp, not this)</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Service exists but NO hook layer. Components call DocumentService directly. CREATE: use-documents.ts hook, /api/admission/documents/route.ts. Wire full chain.</v>
       </c>
       <c r="J39" t="str">
-        <v>omm-dev only</v>
+        <v>Component -&gt; Service (no hook)</v>
+      </c>
+      <c r="K39" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Medium</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gdpi</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
+        <v>Enrollment &gt; Feedback</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Admission process feedback collection. Survey management, response tracking, sentiment analysis.</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Open /feedback -&gt; survey list -&gt; create -&gt; view responses -&gt; analyze sentiment -&gt; export.</v>
       </c>
       <c r="D40" t="str">
-        <v>0 vs 0</v>
+        <v>admission_leads, custom feedback tables</v>
       </c>
       <c r="E40" t="str">
-        <v>0 vs 0</v>
+        <v>feedback-service.ts</v>
       </c>
       <c r="F40" t="str">
-        <v>0 vs 0</v>
+        <v>use-feedback.ts (exists)</v>
       </c>
       <c r="G40" t="str">
-        <v>0 vs 4</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>4</v>
+        <v>None</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Service and hook file exist. Page components call service directly. MISSING: API routes. Wire through hooks -&gt; API -&gt; service.</v>
       </c>
       <c r="J40" t="str">
-        <v>omm-dev only</v>
+        <v>Component -&gt; Service (hook exists but unused)</v>
+      </c>
+      <c r="K40" t="str">
+        <v>P2</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Simple</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>group-dashboard</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
+        <v>Marketing &gt; Remarketing</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Strategic remarketing via digital channels. Audience rules, ad platform sync (Google/Facebook Ads), retargeting, conversion tracking.</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Open /remarketing -&gt; audience rules -&gt; sync to ad platforms -&gt; campaign performance -&gt; conversion attribution.</v>
       </c>
       <c r="D41" t="str">
-        <v>4 vs 4</v>
+        <v>Custom remarketing tables</v>
       </c>
       <c r="E41" t="str">
-        <v>1 vs 1</v>
+        <v>lib/services/marketing/remarketing-service.ts</v>
       </c>
       <c r="F41" t="str">
-        <v>1 vs 1</v>
+        <v>use-remarketing.ts</v>
       </c>
       <c r="G41" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H41">
-        <v>7</v>
-      </c>
-      <c r="I41">
-        <v>7</v>
+        <v>app/api/admission/remarketing/route.ts</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Working</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Service, hooks, API route exist. REQUIRES: ad platform API keys (Google Ads, Facebook Ads). Verify DB tables exist.</v>
       </c>
       <c r="J41" t="str">
-        <v>Fully merged</v>
+        <v>API Route Pattern (service in /marketing/)</v>
+      </c>
+      <c r="K41" t="str">
+        <v>P3</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Complex</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>hostels</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
+        <v>Apply (Public Form)</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Public admission application form. Students apply directly. Auto-creates lead + application records.</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Student visits /admission/apply -&gt; fills form -&gt; submits -&gt; gets confirmation -&gt; lead auto-created.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>admission_leads, admission_applications</v>
+      </c>
+      <c r="E42" t="str">
+        <v>application-service.ts</v>
+      </c>
+      <c r="F42" t="str">
+        <v>index.ts (useApplicationMutations)</v>
+      </c>
+      <c r="G42" t="str">
+        <v>app/api/b2a/admission/route.ts (POST)</v>
+      </c>
+      <c r="H42" t="str">
+        <v>omm-dev only</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Page exists only in omm-dev branch. Merge to main. Needs: public access (no auth), CSRF protection, rate limiting, captcha. Create /api/admission/apply/route.ts.</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Special: public route, no auth</v>
+      </c>
+      <c r="K42" t="str">
+        <v>P1</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Medium</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L42"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D109"/>
+  <cols>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="52.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>MyJKKN Admission CRM - Architecture Reference</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CURRENT ARCHITECTURE (Most Modules)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Layer</v>
+      </c>
+      <c r="B4" t="str">
+        <v>File Location</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Page</v>
+      </c>
+      <c r="B5" t="str">
+        <v>app/(routes)/admission/[module]/page.tsx</v>
+      </c>
+      <c r="C5" t="str">
+        <v>'use client' React component</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Uses hooks for data, shadcn/ui for UI</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Hook</v>
+      </c>
+      <c r="B6" t="str">
+        <v>hooks/admission/use-[module].ts</v>
+      </c>
+      <c r="C6" t="str">
+        <v>React Query (useQuery/useMutation)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>CURRENTLY: Calls service directly</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Service</v>
+      </c>
+      <c r="B7" t="str">
+        <v>lib/services/admission/[module]-service.ts</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Static class with DB methods</v>
+      </c>
+      <c r="D7" t="str">
+        <v>createClientSupabaseClient(), institution-scoped</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Types</v>
+      </c>
+      <c r="B8" t="str">
+        <v>types/admission.ts</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Interfaces for DB columns</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Single file (518 lines)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TARGET ARCHITECTURE (B2A Pattern A)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Layer</v>
+      </c>
+      <c r="B11" t="str">
+        <v>File Location</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Page</v>
+      </c>
+      <c r="B12" t="str">
+        <v>app/(routes)/admission/[module]/page.tsx</v>
+      </c>
+      <c r="C12" t="str">
+        <v>'use client' React component</v>
+      </c>
+      <c r="D12" t="str">
+        <v>No changes needed</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hook</v>
+      </c>
+      <c r="B13" t="str">
+        <v>hooks/admission/use-[module].ts</v>
+      </c>
+      <c r="C13" t="str">
+        <v>React Query hooks</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CHANGE: fetch('/api/...') not Service.method()</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>API Route</v>
+      </c>
+      <c r="B14" t="str">
+        <v>app/api/admission/[module]/route.ts</v>
+      </c>
+      <c r="C14" t="str">
+        <v>withAuth() + service call</v>
+      </c>
+      <c r="D14" t="str">
+        <v>NEW: auth, validation, error mapping</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Service</v>
+      </c>
+      <c r="B15" t="str">
+        <v>lib/services/admission/[module]-service.ts</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Static class with DB methods</v>
+      </c>
+      <c r="D15" t="str">
+        <v>No changes - called by route now</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>B2A MIGRATION STEPS (per module)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Step</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Action</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Example</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>1</v>
       </c>
-      <c r="D42" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E42" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F42" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G42" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
+      <c r="B19" t="str">
+        <v>Create API route file</v>
+      </c>
+      <c r="C19" t="str">
+        <v>app/api/admission/[module]/route.ts</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>2</v>
       </c>
-      <c r="J42" t="str">
-        <v>omm-dev only</v>
+      <c r="B20" t="str">
+        <v>Add withAuth() wrapper</v>
+      </c>
+      <c r="C20" t="str">
+        <v>const { auth } = await withAuth(request);</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>3</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Call service from route</v>
+      </c>
+      <c r="C21" t="str">
+        <v>const data = await Service.getItems(auth.institutionId);</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Return JSON response</v>
+      </c>
+      <c r="C22" t="str">
+        <v>return NextResponse.json({ data, metadata });</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>5</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Update hook to fetch()</v>
+      </c>
+      <c r="C23" t="str">
+        <v>const res = await fetch('/api/admission/[module]');</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>6</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Add OPTIONS handler</v>
+      </c>
+      <c r="C24" t="str">
+        <v>export async function OPTIONS() { ... }</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>7</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Test end-to-end</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Verify auth, data, CRUD</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>EXISTING API ROUTES</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Route Path</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>/api/admission/leads/route.ts</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Leads</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Basic lead ops</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>/api/admission/calls/* (4 routes)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Counselor Calls</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Full CRUD + initiate + stats</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>/api/admission/alerts/route.ts</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Counselor Alerts</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Alert rules CRUD</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>/api/admission/campaigns/roi/route.ts</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Campaign ROI</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ROI analytics</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>/api/admission/campaigns/segments/* (4 routes)</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Segments</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Audience mgmt</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>/api/admission/chat/* (13+ routes)</v>
+      </c>
+      <c r="B34" t="str">
+        <v>WhatsApp Chat</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Most complete</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>/api/admission/chatbot/* (6 routes)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Chatbot</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Config, analytics, knowledge</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>/api/admission/consultants/* (2 routes)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Consultants</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Import + template</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>/api/admission/costs/route.ts</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Costs</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Communication costs</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>/api/admission/email/* (3 routes)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Email</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Send, bulk, logs</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>/api/admission/gdpi/* (4 routes)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>GD-PI</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Sessions, candidates, scores</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>/api/admission/insights/generate/route.ts</v>
+      </c>
+      <c r="B40" t="str">
+        <v>AI Insights</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Generate insights</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>/api/admission/loans/* (4 routes)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Loans</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Applications + partners</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>/api/admission/remarketing/route.ts</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Remarketing</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Audience rules</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>index</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="E43" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F43" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G43" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" t="str">
-        <v>Fully merged</v>
+        <v>/api/admission/settings/whatsapp-numbers/* (4 routes)</v>
+      </c>
+      <c r="B43" t="str">
+        <v>WA Numbers</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Number mgmt</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>insights</v>
-      </c>
-      <c r="B44">
-        <v>2</v>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44" t="str">
-        <v>8 vs 8</v>
-      </c>
-      <c r="E44" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="F44" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="G44" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H44">
-        <v>15</v>
-      </c>
-      <c r="I44">
-        <v>15</v>
-      </c>
-      <c r="J44" t="str">
-        <v>Fully merged</v>
+        <v>/api/admission/voice-agents/* (2 routes)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Voice Agents</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Configs + calls</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>interviews</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E45" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F45" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G45" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>3</v>
-      </c>
-      <c r="J45" t="str">
-        <v>omm-dev only</v>
+        <v>/api/admission/voice-broadcast/route.ts</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Voice Broadcast</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Campaigns</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>lateral-entry</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E46" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F46" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G46" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>5</v>
-      </c>
-      <c r="J46" t="str">
-        <v>omm-dev only</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>lead-scoring</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47" t="str">
-        <v>4 vs 4</v>
-      </c>
-      <c r="E47" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F47" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G47" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H47">
-        <v>6</v>
-      </c>
-      <c r="I47">
-        <v>6</v>
-      </c>
-      <c r="J47" t="str">
-        <v>Fully merged</v>
+        <v>/api/b2a/admission/* (3 routes)</v>
+      </c>
+      <c r="B46" t="str">
+        <v>B2A Bridge</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Legacy bridge</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>leads</v>
-      </c>
-      <c r="B48">
-        <v>3</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48" t="str">
-        <v>4 vs 4</v>
-      </c>
-      <c r="E48" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F48" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G48" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H48">
-        <v>9</v>
-      </c>
-      <c r="I48">
-        <v>9</v>
-      </c>
-      <c r="J48" t="str">
-        <v>Fully merged</v>
+        <v>MODULES NEEDING API ROUTES</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>loans</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E49" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F49" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G49" t="str">
-        <v>0 vs 4</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>7</v>
-      </c>
-      <c r="J49" t="str">
-        <v>omm-dev only</v>
+        <v>Module</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Routes Needed</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Priority</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>marketing/campaigns</v>
-      </c>
-      <c r="B50">
-        <v>4</v>
-      </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E50" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F50" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G50" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="I50">
-        <v>4</v>
-      </c>
-      <c r="J50" t="str">
-        <v>Fully merged</v>
+        <v>Dashboard</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/api/admission/dashboard/route.ts</v>
+      </c>
+      <c r="C50" t="str">
+        <v>P0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>marketing/chat</v>
-      </c>
-      <c r="B51">
-        <v>3</v>
-      </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
-      <c r="D51" t="str">
-        <v>3 vs 3</v>
-      </c>
-      <c r="E51" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F51" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G51" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H51">
-        <v>6</v>
-      </c>
-      <c r="I51">
-        <v>6</v>
-      </c>
-      <c r="J51" t="str">
-        <v>Fully merged</v>
+        <v>Applications</v>
+      </c>
+      <c r="B51" t="str">
+        <v>/api/admission/applications/route.ts + /[id]</v>
+      </c>
+      <c r="C51" t="str">
+        <v>P0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>marketing/chatbot</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E52" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F52" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G52" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
-      </c>
-      <c r="I52">
-        <v>3</v>
-      </c>
-      <c r="J52" t="str">
-        <v>Fully merged</v>
+        <v>Counselors CRUD</v>
+      </c>
+      <c r="B52" t="str">
+        <v>/api/admission/counselors/route.ts + /[id]</v>
+      </c>
+      <c r="C52" t="str">
+        <v>P0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marketing/database</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53" t="str">
-        <v>4 vs 0</v>
-      </c>
-      <c r="E53" t="str">
-        <v>1 vs 0</v>
-      </c>
-      <c r="F53" t="str">
-        <v>1 vs 0</v>
-      </c>
-      <c r="G53" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H53">
-        <v>7</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="str">
-        <v>main only</v>
+        <v>Counselors Daily View</v>
+      </c>
+      <c r="B53" t="str">
+        <v>/api/admission/counselors/daily-view/route.ts</v>
+      </c>
+      <c r="C53" t="str">
+        <v>P0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>marketing/expos</v>
-      </c>
-      <c r="B54">
-        <v>7</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54" t="str">
-        <v>7 vs 0</v>
-      </c>
-      <c r="E54" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F54" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G54" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H54">
-        <v>14</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" t="str">
-        <v>main only</v>
+        <v>Workflows</v>
+      </c>
+      <c r="B54" t="str">
+        <v>/api/admission/settings/workflows/route.ts + /[id]</v>
+      </c>
+      <c r="C54" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>marketing/parent-communication</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="E55" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F55" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G55" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H55">
-        <v>3</v>
-      </c>
-      <c r="I55">
-        <v>3</v>
-      </c>
-      <c r="J55" t="str">
-        <v>Fully merged</v>
+        <v>Assignment Rules</v>
+      </c>
+      <c r="B55" t="str">
+        <v>/api/admission/settings/assignment-rules/route.ts + /[id]</v>
+      </c>
+      <c r="C55" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>marketing/publishers</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="str">
-        <v>3 vs 3</v>
-      </c>
-      <c r="E56" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F56" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G56" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H56">
-        <v>4</v>
-      </c>
-      <c r="I56">
-        <v>4</v>
-      </c>
-      <c r="J56" t="str">
-        <v>Fully merged</v>
+        <v>Scoring Rules</v>
+      </c>
+      <c r="B56" t="str">
+        <v>/api/admission/settings/scoring-rules/route.ts + /[id]</v>
+      </c>
+      <c r="C56" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>marketing/re-engagement</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="E57" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F57" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G57" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H57">
-        <v>3</v>
-      </c>
-      <c r="I57">
-        <v>3</v>
-      </c>
-      <c r="J57" t="str">
-        <v>Fully merged</v>
+        <v>Templates CRUD</v>
+      </c>
+      <c r="B57" t="str">
+        <v>/api/admission/settings/templates/route.ts + /[id]</v>
+      </c>
+      <c r="C57" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>marketing/remarketing</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E58" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F58" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G58" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="J58" t="str">
-        <v>Fully merged</v>
+        <v>Analytics</v>
+      </c>
+      <c r="B58" t="str">
+        <v>/api/admission/analytics/route.ts</v>
+      </c>
+      <c r="C58" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marketing/voice-agents</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E59" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F59" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G59" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-      <c r="J59" t="str">
-        <v>Fully merged</v>
+        <v>Apply (Public)</v>
+      </c>
+      <c r="B59" t="str">
+        <v>/api/admission/apply/route.ts (NO auth)</v>
+      </c>
+      <c r="C59" t="str">
+        <v>P1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marketing/voice-broadcast</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E60" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F60" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G60" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="J60" t="str">
-        <v>Fully merged</v>
+        <v>Sources</v>
+      </c>
+      <c r="B60" t="str">
+        <v>/api/admission/settings/sources/route.ts</v>
+      </c>
+      <c r="C60" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>mcp-tools</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E61" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F61" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G61" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="J61" t="str">
-        <v>Fully merged</v>
+        <v>Workflow Config</v>
+      </c>
+      <c r="B61" t="str">
+        <v>/api/admission/settings/workflow-config/route.ts</v>
+      </c>
+      <c r="C61" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>merit-list</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E62" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F62" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G62" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>5</v>
-      </c>
-      <c r="J62" t="str">
-        <v>omm-dev only</v>
+        <v>Group Dashboard</v>
+      </c>
+      <c r="B62" t="str">
+        <v>/api/admission/group-dashboard/route.ts</v>
+      </c>
+      <c r="C62" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>migration-activity_alert_tables</v>
-      </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E63" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F63" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G63" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="J63" t="str">
-        <v>Fully merged</v>
+        <v>Screening Exam</v>
+      </c>
+      <c r="B63" t="str">
+        <v>/api/admission/screening-exam/route.ts + /[id]</v>
+      </c>
+      <c r="C63" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>migration-add_referral_type</v>
-      </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E64" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F64" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G64" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64" t="str">
-        <v>main only</v>
+        <v>Merit List</v>
+      </c>
+      <c r="B64" t="str">
+        <v>/api/admission/merit-list/route.ts</v>
+      </c>
+      <c r="C64" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>migration-admission_ai_insights_rls</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E65" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F65" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G65" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H65">
-        <v>1</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="J65" t="str">
-        <v>Fully merged</v>
+        <v>Interviews</v>
+      </c>
+      <c r="B65" t="str">
+        <v>/api/admission/interviews/route.ts + /[id]</v>
+      </c>
+      <c r="C65" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>migration-admission_daily_briefings_rls</v>
-      </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E66" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F66" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G66" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H66">
-        <v>1</v>
-      </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
-      <c r="J66" t="str">
-        <v>Fully merged</v>
+        <v>Scholarships</v>
+      </c>
+      <c r="B66" t="str">
+        <v>/api/admission/scholarships/route.ts + /[id]</v>
+      </c>
+      <c r="C66" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>migration-consultant_tables</v>
-      </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E67" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F67" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G67" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H67">
-        <v>1</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-      <c r="J67" t="str">
-        <v>Fully merged</v>
+        <v>Hostels</v>
+      </c>
+      <c r="B67" t="str">
+        <v>/api/admission/hostels/route.ts</v>
+      </c>
+      <c r="C67" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>migration-core_tables</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E68" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F68" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G68" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68">
-        <v>1</v>
-      </c>
-      <c r="J68" t="str">
-        <v>Fully merged</v>
+        <v>Offer Letters</v>
+      </c>
+      <c r="B68" t="str">
+        <v>/api/admission/offer-letters/route.ts + /[id]</v>
+      </c>
+      <c r="C68" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>migration-counselor_daily_view_function</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E69" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F69" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G69" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="I69">
-        <v>1</v>
-      </c>
-      <c r="J69" t="str">
-        <v>Fully merged</v>
+        <v>Seat Confirmation</v>
+      </c>
+      <c r="B69" t="str">
+        <v>/api/admission/seat-confirmation/route.ts</v>
+      </c>
+      <c r="C69" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>migration-enums_and_functions</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E70" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F70" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G70" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
-      </c>
-      <c r="J70" t="str">
-        <v>Fully merged</v>
+        <v>Lateral Entry</v>
+      </c>
+      <c r="B70" t="str">
+        <v>/api/admission/lateral-entry/route.ts</v>
+      </c>
+      <c r="C70" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>migration-rls_policies</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E71" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F71" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G71" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="J71" t="str">
-        <v>Fully merged</v>
+        <v>Documents</v>
+      </c>
+      <c r="B71" t="str">
+        <v>/api/admission/documents/route.ts + /[id]</v>
+      </c>
+      <c r="C71" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>migration-triggers_and_views</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E72" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F72" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G72" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="J72" t="str">
-        <v>Fully merged</v>
+        <v>Feedback</v>
+      </c>
+      <c r="B72" t="str">
+        <v>/api/admission/feedback/route.ts</v>
+      </c>
+      <c r="C72" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>migration-wa_conversations_messages</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E73" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F73" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G73" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73">
-        <v>1</v>
-      </c>
-      <c r="J73" t="str">
-        <v>Fully merged</v>
+        <v>Parent Communication</v>
+      </c>
+      <c r="B73" t="str">
+        <v>/api/admission/parent-communication/route.ts</v>
+      </c>
+      <c r="C73" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>migrations</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E74" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F74" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G74" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H74">
-        <v>3</v>
-      </c>
-      <c r="I74">
-        <v>9</v>
-      </c>
-      <c r="J74" t="str">
-        <v>Partially merged</v>
+        <v>Re-engagement</v>
+      </c>
+      <c r="B74" t="str">
+        <v>/api/admission/re-engagement/route.ts</v>
+      </c>
+      <c r="C74" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>naac-report</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E75" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F75" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G75" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H75">
-        <v>2</v>
-      </c>
-      <c r="I75">
-        <v>2</v>
-      </c>
-      <c r="J75" t="str">
-        <v>Fully merged</v>
+        <v>Phone Validation</v>
+      </c>
+      <c r="B75" t="str">
+        <v>/api/admission/data-quality/phone-validation/route.ts</v>
+      </c>
+      <c r="C75" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>offer-letter</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E76" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F76" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G76" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>5</v>
-      </c>
-      <c r="J76" t="str">
-        <v>omm-dev only</v>
+        <v>Deduplication</v>
+      </c>
+      <c r="B76" t="str">
+        <v>/api/admission/data-quality/deduplication/route.ts</v>
+      </c>
+      <c r="C76" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>other</v>
-      </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E77" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F77" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G77" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
-      <c r="J77" t="str">
-        <v>Fully merged</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>parent-communication</v>
-      </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E78" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F78" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G78" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H78">
-        <v>2</v>
-      </c>
-      <c r="I78">
-        <v>5</v>
-      </c>
-      <c r="J78" t="str">
-        <v>Partially merged</v>
+        <v>Data Profiling</v>
+      </c>
+      <c r="B77" t="str">
+        <v>/api/admission/data-quality/data-profiling/route.ts</v>
+      </c>
+      <c r="C77" t="str">
+        <v>P2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>phone-validation</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E79" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F79" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G79" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-      <c r="J79" t="str">
-        <v>omm-dev only</v>
+        <v>DATABASE TABLES</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>process-excellence</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="E80" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F80" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G80" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>1</v>
-      </c>
-      <c r="J80" t="str">
-        <v>omm-dev only</v>
+        <v>Table Name</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Cols</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Primary Usage</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>publishers</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" t="str">
-        <v>0 vs 3</v>
-      </c>
-      <c r="E81" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F81" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G81" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81">
-        <v>4</v>
-      </c>
-      <c r="J81" t="str">
-        <v>omm-dev only</v>
+        <v>admission_leads</v>
+      </c>
+      <c r="B81" t="str">
+        <v>61</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Core - all modules reference this</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>re-engagement</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E82" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F82" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G82" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H82">
-        <v>2</v>
-      </c>
-      <c r="I82">
-        <v>5</v>
-      </c>
-      <c r="J82" t="str">
-        <v>Partially merged</v>
+        <v>admission_lead_activities</v>
+      </c>
+      <c r="B82" t="str">
+        <v>9</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Activities, Timeline</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>remarketing</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E83" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F83" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G83" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H83">
-        <v>2</v>
-      </c>
-      <c r="I83">
-        <v>3</v>
-      </c>
-      <c r="J83" t="str">
-        <v>Partially merged</v>
+        <v>admission_lead_stage_history</v>
+      </c>
+      <c r="B83" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Funnel, Analytics</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>reminders</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E84" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F84" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G84" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H84">
-        <v>2</v>
-      </c>
-      <c r="I84">
-        <v>2</v>
-      </c>
-      <c r="J84" t="str">
-        <v>Fully merged</v>
+        <v>admission_lead_scores</v>
+      </c>
+      <c r="B84" t="str">
+        <v>~6</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Lead Scoring, Merit List</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>response-personalizer</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="E85" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F85" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G85" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H85">
-        <v>1</v>
-      </c>
-      <c r="I85">
-        <v>1</v>
-      </c>
-      <c r="J85" t="str">
-        <v>Fully merged</v>
+        <v>admission_counselors</v>
+      </c>
+      <c r="B85" t="str">
+        <v>9</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Counselors, Assignment</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>scholarships</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="C86">
-        <v>3</v>
-      </c>
-      <c r="D86" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E86" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F86" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G86" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>4</v>
-      </c>
-      <c r="J86" t="str">
-        <v>omm-dev only</v>
+        <v>admission_applications</v>
+      </c>
+      <c r="B86" t="str">
+        <v>~20</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Applications</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>scoring-rules</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="str">
-        <v>0 vs 3</v>
-      </c>
-      <c r="E87" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F87" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G87" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <v>6</v>
-      </c>
-      <c r="J87" t="str">
-        <v>omm-dev only</v>
+        <v>admission_communication_templates</v>
+      </c>
+      <c r="B87" t="str">
+        <v>~12</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Templates, Chat</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>screening-exam</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E88" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F88" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G88" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>3</v>
-      </c>
-      <c r="J88" t="str">
-        <v>omm-dev only</v>
+        <v>admission_sms_logs</v>
+      </c>
+      <c r="B88" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C88" t="str">
+        <v>SMS campaigns</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>seat-confirmation</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="str">
-        <v>0 vs 3</v>
-      </c>
-      <c r="E89" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="F89" t="str">
-        <v>0 vs 1</v>
-      </c>
-      <c r="G89" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>6</v>
-      </c>
-      <c r="J89" t="str">
-        <v>omm-dev only</v>
+        <v>admission_whatsapp_logs</v>
+      </c>
+      <c r="B89" t="str">
+        <v>~12</v>
+      </c>
+      <c r="C89" t="str">
+        <v>WA chat/campaigns</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>settings</v>
-      </c>
-      <c r="B90">
-        <v>1</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E90" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F90" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G90" t="str">
-        <v>4 vs 4</v>
-      </c>
-      <c r="H90">
-        <v>6</v>
-      </c>
-      <c r="I90">
-        <v>6</v>
-      </c>
-      <c r="J90" t="str">
-        <v>Fully merged</v>
+        <v>admission_whatsapp_campaign_logs</v>
+      </c>
+      <c r="B90" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Bulk WA campaigns</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>settings/assignment-rules</v>
-      </c>
-      <c r="B91">
-        <v>1</v>
-      </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91" t="str">
-        <v>3 vs 3</v>
-      </c>
-      <c r="E91" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F91" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G91" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H91">
-        <v>4</v>
-      </c>
-      <c r="I91">
-        <v>4</v>
-      </c>
-      <c r="J91" t="str">
-        <v>Fully merged</v>
+        <v>admission_campaign_logs</v>
+      </c>
+      <c r="B91" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Campaign execution</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>settings/sources</v>
-      </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="E92" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F92" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G92" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H92">
-        <v>3</v>
-      </c>
-      <c r="I92">
-        <v>3</v>
-      </c>
-      <c r="J92" t="str">
-        <v>Fully merged</v>
+        <v>admission_campaign_queue</v>
+      </c>
+      <c r="B92" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Campaign processor</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>settings/templates</v>
-      </c>
-      <c r="B93">
-        <v>4</v>
-      </c>
-      <c r="C93">
-        <v>4</v>
-      </c>
-      <c r="D93" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E93" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F93" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G93" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H93">
-        <v>4</v>
-      </c>
-      <c r="I93">
-        <v>4</v>
-      </c>
-      <c r="J93" t="str">
-        <v>Fully merged</v>
+        <v>admission_workflows</v>
+      </c>
+      <c r="B93" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Workflow automation</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>settings/whatsapp-numbers</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94" t="str">
-        <v>1 vs 0</v>
-      </c>
-      <c r="E94" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F94" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G94" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H94">
-        <v>2</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
-      </c>
-      <c r="J94" t="str">
-        <v>Partially merged</v>
+        <v>admission_workflow_executions</v>
+      </c>
+      <c r="B94" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Workflow audit</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>settings/workflow-config</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95" t="str">
-        <v>5 vs 5</v>
-      </c>
-      <c r="E95" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F95" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G95" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H95">
-        <v>6</v>
-      </c>
-      <c r="I95">
-        <v>6</v>
-      </c>
-      <c r="J95" t="str">
-        <v>Fully merged</v>
+        <v>admission_workflow_configs</v>
+      </c>
+      <c r="B95" t="str">
+        <v>~6</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Engine config</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>settings/workflows</v>
-      </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E96" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F96" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G96" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96" t="str">
-        <v>Fully merged</v>
+        <v>admission_assignment_rules</v>
+      </c>
+      <c r="B96" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Auto-assignment</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sms-campaign</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-      <c r="D97" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E97" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F97" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G97" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97">
-        <v>2</v>
-      </c>
-      <c r="J97" t="str">
-        <v>Fully merged</v>
+        <v>admission_scoring_rules</v>
+      </c>
+      <c r="B97" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Lead scoring</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>sources</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98" t="str">
-        <v>0 vs 2</v>
-      </c>
-      <c r="E98" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F98" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G98" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H98">
-        <v>2</v>
-      </c>
-      <c r="I98">
-        <v>5</v>
-      </c>
-      <c r="J98" t="str">
-        <v>Partially merged</v>
+        <v>admission_gdpi_sessions</v>
+      </c>
+      <c r="B98" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C98" t="str">
+        <v>GD-PI sessions</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>status</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99" t="str">
-        <v>0 vs 3</v>
-      </c>
-      <c r="E99" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F99" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G99" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H99">
-        <v>2</v>
-      </c>
-      <c r="I99">
-        <v>6</v>
-      </c>
-      <c r="J99" t="str">
-        <v>Partially merged</v>
+        <v>admission_gdpi_candidates</v>
+      </c>
+      <c r="B99" t="str">
+        <v>~6</v>
+      </c>
+      <c r="C99" t="str">
+        <v>GD-PI candidates</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>templates</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="C100">
-        <v>4</v>
-      </c>
-      <c r="D100" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E100" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F100" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="G100" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H100">
-        <v>3</v>
-      </c>
-      <c r="I100">
-        <v>7</v>
-      </c>
-      <c r="J100" t="str">
-        <v>Partially merged</v>
+        <v>admission_gdpi_scores</v>
+      </c>
+      <c r="B100" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C100" t="str">
+        <v>GD-PI scoring</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>tqm-metrics</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E101" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F101" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G101" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H101">
-        <v>2</v>
-      </c>
-      <c r="I101">
-        <v>2</v>
-      </c>
-      <c r="J101" t="str">
-        <v>Fully merged</v>
+        <v>admission_loan_applications</v>
+      </c>
+      <c r="B101" t="str">
+        <v>~15</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Loan tracking</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>types</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
-      <c r="D102" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E102" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F102" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="G102" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H102">
-        <v>2</v>
-      </c>
-      <c r="I102">
-        <v>2</v>
-      </c>
-      <c r="J102" t="str">
-        <v>Fully merged</v>
+        <v>admission_loan_partners</v>
+      </c>
+      <c r="B102" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Bank/NBFC partners</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>voice-agents</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E103" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F103" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G103" t="str">
-        <v>2 vs 2</v>
-      </c>
-      <c r="H103">
-        <v>3</v>
-      </c>
-      <c r="I103">
-        <v>4</v>
-      </c>
-      <c r="J103" t="str">
-        <v>Partially merged</v>
+        <v>admission_payments</v>
+      </c>
+      <c r="B103" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Seat confirmation</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>voice-broadcast</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-      <c r="C104">
-        <v>1</v>
-      </c>
-      <c r="D104" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E104" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F104" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G104" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="H104">
-        <v>2</v>
-      </c>
-      <c r="I104">
-        <v>3</v>
-      </c>
-      <c r="J104" t="str">
-        <v>Partially merged</v>
+        <v>admission_ai_insights</v>
+      </c>
+      <c r="B104" t="str">
+        <v>~12</v>
+      </c>
+      <c r="C104" t="str">
+        <v>AI insights</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>whatsapp-campaign</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-      <c r="C105">
-        <v>0</v>
-      </c>
-      <c r="D105" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E105" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F105" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G105" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H105">
-        <v>2</v>
-      </c>
-      <c r="I105">
-        <v>2</v>
-      </c>
-      <c r="J105" t="str">
-        <v>Fully merged</v>
+        <v>admission_action_executions</v>
+      </c>
+      <c r="B105" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Insight actions</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>whatsapp-personal</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-      <c r="C106">
-        <v>0</v>
-      </c>
-      <c r="D106" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E106" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="F106" t="str">
-        <v>1 vs 0</v>
-      </c>
-      <c r="G106" t="str">
-        <v>7 vs 0</v>
-      </c>
-      <c r="H106">
-        <v>8</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106" t="str">
-        <v>main only</v>
+        <v>admission_daily_briefings</v>
+      </c>
+      <c r="B106" t="str">
+        <v>~10</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Counselor briefings</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>workflow-config</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-      <c r="C107">
-        <v>1</v>
-      </c>
-      <c r="D107" t="str">
-        <v>0 vs 5</v>
-      </c>
-      <c r="E107" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F107" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G107" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H107">
-        <v>2</v>
-      </c>
-      <c r="I107">
-        <v>8</v>
-      </c>
-      <c r="J107" t="str">
-        <v>Partially merged</v>
+        <v>admission_drip_sequences</v>
+      </c>
+      <c r="B107" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Drip campaigns</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>workflows</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="C108">
-        <v>1</v>
-      </c>
-      <c r="D108" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="E108" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="F108" t="str">
-        <v>1 vs 1</v>
-      </c>
-      <c r="G108" t="str">
-        <v>0 vs 0</v>
-      </c>
-      <c r="H108">
-        <v>2</v>
-      </c>
-      <c r="I108">
-        <v>3</v>
-      </c>
-      <c r="J108" t="str">
-        <v>Partially merged</v>
+        <v>admission_email_logs</v>
+      </c>
+      <c r="B108" t="str">
+        <v>~8</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Email campaigns</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>education_consultants</v>
+      </c>
+      <c r="B109" t="str">
+        <v>57</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Consultants/Publishers</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D109"/>
   </ignoredErrors>
 </worksheet>
 </file>